--- a/data/trans_camb/P2A_enfcro_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P2A_enfcro_R-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 24,27</t>
+          <t>-1,22; 26,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 23,37</t>
+          <t>-2,16; 23,26</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>59,01; 75,78</t>
+          <t>59,02; 75,9</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-12,63; 14,57</t>
+          <t>-13,25; 12,45</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,8; 16,8</t>
+          <t>-8,23; 16,92</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>54,88; 72,4</t>
+          <t>52,6; 72,54</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 16,35</t>
+          <t>-3,73; 14,69</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 16,27</t>
+          <t>-1,84; 16,71</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>59,42; 71,46</t>
+          <t>59,43; 72,24</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,51; 98,74</t>
+          <t>-3,48; 109,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-10,64; 94,46</t>
+          <t>-6,12; 95,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>150,42; 334,75</t>
+          <t>152,32; 336,43</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-31,13; 53,24</t>
+          <t>-32,8; 45,38</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-22,23; 57,08</t>
+          <t>-21,41; 61,69</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>124,9; 270,6</t>
+          <t>117,11; 279,3</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-8,75; 59,22</t>
+          <t>-10,71; 54,59</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-4,82; 59,5</t>
+          <t>-4,97; 61,49</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>152,97; 265,19</t>
+          <t>153,02; 277,66</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-13,96; 12,82</t>
+          <t>-14,6; 13,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-22,09; 3,41</t>
+          <t>-22,18; 2,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>41,78; 62,85</t>
+          <t>42,78; 62,79</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-15,17; 12,12</t>
+          <t>-14,83; 11,6</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-17,41; 6,83</t>
+          <t>-17,53; 7,33</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>42,35; 61,97</t>
+          <t>41,65; 61,62</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-10,39; 8,67</t>
+          <t>-10,81; 7,93</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-15,47; 2,39</t>
+          <t>-16,05; 1,9</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>45,03; 59,98</t>
+          <t>45,58; 59,97</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-27,95; 36,44</t>
+          <t>-29,94; 36,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-43,3; 9,41</t>
+          <t>-44,39; 8,12</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>76,47; 181,08</t>
+          <t>79,55; 178,52</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-28,64; 29,72</t>
+          <t>-28,25; 30,46</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-33,98; 17,23</t>
+          <t>-33,1; 18,05</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,15; 170,11</t>
+          <t>74,74; 169,36</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-21,42; 21,19</t>
+          <t>-21,91; 19,86</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-31,02; 5,64</t>
+          <t>-32,19; 4,35</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>86,26; 157,08</t>
+          <t>86,76; 155,04</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,18; 30,76</t>
+          <t>3,43; 31,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,59; 22,79</t>
+          <t>-6,43; 22,21</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>50,83; 74,19</t>
+          <t>49,54; 73,47</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,39; 19,25</t>
+          <t>-5,57; 20,64</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,25; 17,52</t>
+          <t>-8,55; 16,76</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>51,05; 71,71</t>
+          <t>52,88; 71,9</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,23; 21,48</t>
+          <t>2,72; 21,8</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 15,54</t>
+          <t>-4,56; 15,2</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>56,06; 70,41</t>
+          <t>54,91; 69,73</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9,76; 149,75</t>
+          <t>9,52; 137,93</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-18,6; 103,52</t>
+          <t>-18,27; 100,23</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>129,91; 353,24</t>
+          <t>128,03; 350,12</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-15,89; 70,12</t>
+          <t>-15,46; 73,08</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-21,49; 63,47</t>
+          <t>-21,65; 60,18</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>118,98; 274,34</t>
+          <t>127,15; 278,7</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,64; 79,29</t>
+          <t>7,39; 78,77</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-10,57; 56,53</t>
+          <t>-11,76; 54,17</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>147,39; 269,9</t>
+          <t>143,62; 264,79</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 18,77</t>
+          <t>0,33; 18,29</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 14,29</t>
+          <t>-3,56; 14,21</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>50,14; 63,95</t>
+          <t>50,38; 63,85</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,02; 19,51</t>
+          <t>2,54; 20,34</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-15,23; 1,64</t>
+          <t>-15,3; 1,7</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>44,68; 58,92</t>
+          <t>45,07; 59,23</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,79; 16,29</t>
+          <t>3,8; 16,78</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-7,46; 4,96</t>
+          <t>-7,39; 5,32</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>50,11; 59,71</t>
+          <t>50,03; 59,62</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 52,88</t>
+          <t>0,46; 52,44</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-7,97; 40,59</t>
+          <t>-8,13; 39,7</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>109,72; 190,07</t>
+          <t>108,76; 187,4</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,78; 51,78</t>
+          <t>5,44; 54,77</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-33,23; 3,92</t>
+          <t>-32,33; 4,94</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>92,59; 163,12</t>
+          <t>94,47; 161,98</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,75; 43,34</t>
+          <t>8,44; 43,56</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-16,75; 13,88</t>
+          <t>-16,92; 13,74</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>109,88; 163,54</t>
+          <t>109,63; 160,26</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-12,44; 14,05</t>
+          <t>-14,23; 12,26</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-10,38; 14,06</t>
+          <t>-10,8; 14,64</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>34,76; 55,57</t>
+          <t>35,01; 56,35</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 22,09</t>
+          <t>-1,01; 22,15</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-6,76; 17,73</t>
+          <t>-7,18; 18,87</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>32,56; 53,42</t>
+          <t>33,13; 53,26</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 13,75</t>
+          <t>-4,01; 13,41</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-5,76; 12,89</t>
+          <t>-4,44; 12,86</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>36,56; 51,34</t>
+          <t>36,34; 51,54</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-24,62; 38,69</t>
+          <t>-27,5; 33,3</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-20,11; 39,09</t>
+          <t>-20,85; 39,95</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>65,5; 156,65</t>
+          <t>65,93; 162,74</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-5,52; 53,8</t>
+          <t>-2,1; 55,48</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-13,42; 42,85</t>
+          <t>-12,38; 46,69</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>58,73; 135,69</t>
+          <t>60,8; 136,87</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-8,74; 32,89</t>
+          <t>-7,73; 33,16</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-10,96; 31,06</t>
+          <t>-8,42; 32,27</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>69,73; 131,07</t>
+          <t>70,32; 132,46</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-10,36; 19,03</t>
+          <t>-10,49; 17,16</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-18,3; 9,67</t>
+          <t>-18,87; 7,83</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>32,04; 53,43</t>
+          <t>30,63; 51,72</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-18,39; 9,34</t>
+          <t>-16,9; 8,76</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-24,97; 3,13</t>
+          <t>-25,93; 1,9</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>27,15; 48,43</t>
+          <t>26,53; 48,63</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-10,2; 9,96</t>
+          <t>-11,24; 9,46</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-18,09; 1,69</t>
+          <t>-18,09; 0,09</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>32,34; 48,02</t>
+          <t>32,24; 47,62</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-18,36; 44,35</t>
+          <t>-19,57; 39,63</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-34,32; 21,76</t>
+          <t>-33,99; 17,15</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>54,56; 126,21</t>
+          <t>51,53; 123,54</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-30,29; 19,26</t>
+          <t>-28,36; 18,41</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-42,09; 6,64</t>
+          <t>-42,49; 4,37</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>43,38; 105,94</t>
+          <t>44,17; 107,64</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-18,18; 20,59</t>
+          <t>-19,39; 19,39</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-32,6; 3,74</t>
+          <t>-32,88; 0,18</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>56,35; 106,31</t>
+          <t>56,59; 104,24</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>1,55; 12,13</t>
+          <t>1,59; 11,97</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 7,78</t>
+          <t>-2,43; 7,57</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>51,32; 59,31</t>
+          <t>51,47; 59,22</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,47; 10,19</t>
+          <t>-0,39; 10,08</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-6,23; 3,26</t>
+          <t>-6,99; 2,69</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>47,95; 55,72</t>
+          <t>48,13; 55,9</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,55; 9,69</t>
+          <t>2,46; 9,71</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 3,81</t>
+          <t>-3,13; 3,89</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>51,0; 56,22</t>
+          <t>50,7; 56,22</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>3,95; 32,29</t>
+          <t>3,79; 32,24</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 20,77</t>
+          <t>-5,49; 20,43</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>119,36; 162,04</t>
+          <t>117,57; 161,53</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1,0; 25,2</t>
+          <t>-1,04; 24,87</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-13,92; 8,03</t>
+          <t>-15,62; 6,39</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>103,15; 140,18</t>
+          <t>103,19; 140,76</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>5,85; 24,28</t>
+          <t>5,8; 24,35</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-7,24; 9,48</t>
+          <t>-7,28; 9,74</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>117,51; 144,58</t>
+          <t>115,7; 144,52</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_enfcro_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P2A_enfcro_R-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 26,76</t>
+          <t>-0,43; 26,84</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 23,26</t>
+          <t>-3,04; 23,6</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>59,02; 75,9</t>
+          <t>59,68; 76,34</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-13,25; 12,45</t>
+          <t>-13,75; 13,02</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,23; 16,92</t>
+          <t>-8,72; 17,46</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>52,6; 72,54</t>
+          <t>53,89; 72,31</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 14,69</t>
+          <t>-2,83; 15,84</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 16,71</t>
+          <t>-1,12; 17,26</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>59,43; 72,24</t>
+          <t>59,66; 71,92</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 109,64</t>
+          <t>-1,83; 113,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,12; 95,1</t>
+          <t>-8,78; 96,03</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>152,32; 336,43</t>
+          <t>157,24; 342,48</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-32,8; 45,38</t>
+          <t>-34,32; 44,67</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-21,41; 61,69</t>
+          <t>-20,7; 59,92</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>117,11; 279,3</t>
+          <t>120,66; 270,78</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-10,71; 54,59</t>
+          <t>-7,8; 59,77</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-4,97; 61,49</t>
+          <t>-3,21; 62,06</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>153,02; 277,66</t>
+          <t>154,97; 271,3</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-14,6; 13,44</t>
+          <t>-14,55; 13,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-22,18; 2,98</t>
+          <t>-21,49; 3,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>42,78; 62,79</t>
+          <t>42,63; 62,49</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-14,83; 11,6</t>
+          <t>-16,45; 11,37</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-17,53; 7,33</t>
+          <t>-18,92; 6,32</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>41,65; 61,62</t>
+          <t>42,26; 60,89</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-10,81; 7,93</t>
+          <t>-11,51; 7,89</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-16,05; 1,9</t>
+          <t>-15,65; 2,28</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>45,58; 59,97</t>
+          <t>44,89; 59,38</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-29,94; 36,94</t>
+          <t>-30,44; 34,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-44,39; 8,12</t>
+          <t>-42,9; 9,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>79,55; 178,52</t>
+          <t>78,12; 173,92</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-28,25; 30,46</t>
+          <t>-30,02; 29,13</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-33,1; 18,05</t>
+          <t>-35,12; 15,71</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,74; 169,36</t>
+          <t>75,28; 161,57</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-21,91; 19,86</t>
+          <t>-23,3; 18,39</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-32,19; 4,35</t>
+          <t>-31,69; 5,37</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>86,76; 155,04</t>
+          <t>86,45; 152,6</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,43; 31,07</t>
+          <t>2,37; 31,06</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,43; 22,21</t>
+          <t>-6,75; 22,81</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>49,54; 73,47</t>
+          <t>50,92; 73,99</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,57; 20,64</t>
+          <t>-5,49; 20,03</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,55; 16,76</t>
+          <t>-8,63; 16,02</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>52,88; 71,9</t>
+          <t>52,48; 71,3</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,72; 21,8</t>
+          <t>3,42; 21,88</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,56; 15,2</t>
+          <t>-3,77; 15,72</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>54,91; 69,73</t>
+          <t>54,59; 69,67</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9,52; 137,93</t>
+          <t>5,41; 139,09</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-18,27; 100,23</t>
+          <t>-19,54; 108,01</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>128,03; 350,12</t>
+          <t>131,85; 344,96</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-15,46; 73,08</t>
+          <t>-14,66; 64,81</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-21,65; 60,18</t>
+          <t>-21,83; 56,56</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>127,15; 278,7</t>
+          <t>124,88; 270,02</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,39; 78,77</t>
+          <t>9,11; 79,81</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-11,76; 54,17</t>
+          <t>-10,63; 55,5</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>143,62; 264,79</t>
+          <t>140,91; 256,21</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,33; 18,29</t>
+          <t>-1,06; 18,72</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 14,21</t>
+          <t>-4,54; 13,85</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>50,38; 63,85</t>
+          <t>51,23; 64,85</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,54; 20,34</t>
+          <t>1,71; 21,04</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-15,3; 1,7</t>
+          <t>-15,71; 1,74</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>45,07; 59,23</t>
+          <t>45,66; 60,2</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,8; 16,78</t>
+          <t>3,61; 16,36</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-7,39; 5,32</t>
+          <t>-7,59; 5,26</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>50,03; 59,62</t>
+          <t>49,61; 59,67</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,46; 52,44</t>
+          <t>-2,94; 52,08</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-8,13; 39,7</t>
+          <t>-10,07; 38,77</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>108,76; 187,4</t>
+          <t>110,99; 195,19</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5,44; 54,77</t>
+          <t>3,67; 58,38</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-32,33; 4,94</t>
+          <t>-34,67; 4,56</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>94,47; 161,98</t>
+          <t>95,49; 170,3</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,44; 43,56</t>
+          <t>7,96; 43,65</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-16,92; 13,74</t>
+          <t>-17,25; 14,07</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>109,63; 160,26</t>
+          <t>108,18; 162,04</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-14,23; 12,26</t>
+          <t>-12,84; 13,02</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-10,8; 14,64</t>
+          <t>-10,83; 14,34</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>35,01; 56,35</t>
+          <t>34,26; 55,05</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 22,15</t>
+          <t>-2,26; 21,95</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-7,18; 18,87</t>
+          <t>-4,08; 18,55</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>33,13; 53,26</t>
+          <t>32,41; 52,71</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 13,41</t>
+          <t>-4,16; 13,61</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 12,86</t>
+          <t>-4,47; 13,14</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>36,34; 51,54</t>
+          <t>36,45; 50,34</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-27,5; 33,3</t>
+          <t>-25,54; 35,63</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-20,85; 39,95</t>
+          <t>-20,58; 39,41</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>65,93; 162,74</t>
+          <t>64,48; 153,52</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 55,48</t>
+          <t>-4,02; 54,11</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-12,38; 46,69</t>
+          <t>-8,06; 46,3</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>60,8; 136,87</t>
+          <t>58,94; 136,29</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-7,73; 33,16</t>
+          <t>-8,2; 33,08</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-8,42; 32,27</t>
+          <t>-8,96; 32,0</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>70,32; 132,46</t>
+          <t>71,24; 126,7</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-10,49; 17,16</t>
+          <t>-10,86; 20,01</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-18,87; 7,83</t>
+          <t>-19,08; 7,86</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>30,63; 51,72</t>
+          <t>31,03; 52,6</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-16,9; 8,76</t>
+          <t>-17,23; 8,82</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-25,93; 1,9</t>
+          <t>-25,62; 2,08</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>26,53; 48,63</t>
+          <t>27,38; 48,66</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-11,24; 9,46</t>
+          <t>-10,71; 9,1</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-18,09; 0,09</t>
+          <t>-17,95; 1,99</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>32,24; 47,62</t>
+          <t>31,13; 48,0</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-19,57; 39,63</t>
+          <t>-19,68; 46,65</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-33,99; 17,15</t>
+          <t>-34,39; 17,88</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>51,53; 123,54</t>
+          <t>54,44; 127,23</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-28,36; 18,41</t>
+          <t>-29,28; 18,35</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-42,49; 4,37</t>
+          <t>-43,45; 3,98</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>44,17; 107,64</t>
+          <t>45,24; 108,41</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-19,39; 19,39</t>
+          <t>-19,0; 20,08</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-32,88; 0,18</t>
+          <t>-32,36; 3,81</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>56,59; 104,24</t>
+          <t>53,12; 105,73</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>1,59; 11,97</t>
+          <t>1,5; 11,61</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 7,57</t>
+          <t>-2,54; 7,3</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>51,47; 59,22</t>
+          <t>51,67; 59,27</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 10,08</t>
+          <t>0,42; 10,41</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-6,99; 2,69</t>
+          <t>-6,65; 3,11</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>48,13; 55,9</t>
+          <t>48,22; 55,47</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,46; 9,71</t>
+          <t>2,56; 9,8</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 3,89</t>
+          <t>-3,15; 3,59</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>50,7; 56,22</t>
+          <t>50,76; 56,29</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>3,79; 32,24</t>
+          <t>3,61; 30,65</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-5,49; 20,43</t>
+          <t>-6,07; 19,36</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>117,57; 161,53</t>
+          <t>119,75; 162,79</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 24,87</t>
+          <t>0,96; 25,44</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-15,62; 6,39</t>
+          <t>-14,65; 7,66</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>103,19; 140,76</t>
+          <t>104,89; 139,51</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>5,8; 24,35</t>
+          <t>6,19; 24,88</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-7,28; 9,74</t>
+          <t>-7,41; 9,16</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>115,7; 144,52</t>
+          <t>116,14; 144,32</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_enfcro_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P2A_enfcro_R-Clase-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-0,49</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4,52</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>63,75</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>12,44</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>10,57</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>67,96</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-0,49</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>4,52</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>63,8</t>
+          <t>67,79</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>66,01</t>
+          <t>65,9</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 26,84</t>
+          <t>-12,63; 14,57</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 23,6</t>
+          <t>-8,8; 16,8</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>59,68; 76,34</t>
+          <t>54,53; 72,38</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-13,75; 13,02</t>
+          <t>-2,36; 24,27</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,72; 17,46</t>
+          <t>-3,58; 23,37</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>53,89; 72,31</t>
+          <t>58,71; 75,54</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 15,84</t>
+          <t>-2,99; 16,35</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 17,26</t>
+          <t>-1,66; 16,27</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>59,66; 71,92</t>
+          <t>59,19; 71,36</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-1,43%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>13,08%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>184,72%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>41,07%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>34,88%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>224,31%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-1,43%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>13,08%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>184,85%</t>
+          <t>223,74%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>204,46%</t>
+          <t>204,13%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 113,1</t>
+          <t>-31,13; 53,24</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-8,78; 96,03</t>
+          <t>-22,23; 57,08</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>157,24; 342,48</t>
+          <t>124,87; 271,28</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-34,32; 44,67</t>
+          <t>-6,51; 98,74</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-20,7; 59,92</t>
+          <t>-10,64; 94,46</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>120,66; 270,78</t>
+          <t>150,23; 334,77</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-7,8; 59,77</t>
+          <t>-8,75; 59,22</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 62,06</t>
+          <t>-4,82; 59,5</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>154,97; 271,3</t>
+          <t>152,76; 263,96</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-1,73</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-5,44</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>51,65</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-1,15</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-9,2</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>53,33</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-1,73</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-5,44</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>51,64</t>
+          <t>53,21</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>52,5</t>
+          <t>52,43</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-14,55; 13,04</t>
+          <t>-15,17; 12,12</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-21,49; 3,84</t>
+          <t>-17,41; 6,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>42,63; 62,49</t>
+          <t>42,08; 61,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-16,45; 11,37</t>
+          <t>-13,96; 12,82</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-18,92; 6,32</t>
+          <t>-22,09; 3,41</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>42,26; 60,89</t>
+          <t>41,3; 62,72</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-11,51; 7,89</t>
+          <t>-10,39; 8,67</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-15,65; 2,28</t>
+          <t>-15,47; 2,39</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>44,89; 59,38</t>
+          <t>44,92; 59,79</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-3,7%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-11,64%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>110,45%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-2,6%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-20,85%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>120,9%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-3,7%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-11,64%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>110,43%</t>
+          <t>120,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>115,57%</t>
+          <t>115,42%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-30,44; 34,85</t>
+          <t>-28,64; 29,72</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-42,9; 9,94</t>
+          <t>-33,98; 17,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>78,12; 173,92</t>
+          <t>76,33; 170,35</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-30,02; 29,13</t>
+          <t>-27,95; 36,44</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-35,12; 15,71</t>
+          <t>-43,3; 9,41</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,28; 161,57</t>
+          <t>75,86; 180,5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-23,3; 18,39</t>
+          <t>-21,42; 21,19</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-31,69; 5,37</t>
+          <t>-31,02; 5,64</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>86,45; 152,6</t>
+          <t>86,06; 156,71</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>6,72</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>3,56</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>62,75</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>17,81</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>8,14</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>63,76</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>6,72</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>3,56</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>62,82</t>
+          <t>63,97</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>63,06</t>
+          <t>63,01</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,37; 31,06</t>
+          <t>-6,39; 19,25</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,75; 22,81</t>
+          <t>-8,25; 17,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>50,92; 73,99</t>
+          <t>51,17; 71,72</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,49; 20,03</t>
+          <t>3,18; 30,76</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,63; 16,02</t>
+          <t>-6,59; 22,79</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>52,48; 71,3</t>
+          <t>51,23; 74,4</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,42; 21,88</t>
+          <t>2,23; 21,48</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 15,72</t>
+          <t>-3,77; 15,54</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>54,59; 69,67</t>
+          <t>56,0; 70,43</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>19,84%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>10,5%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>185,17%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>60,63%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>27,7%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>217,05%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>19,84%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>10,5%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>185,36%</t>
+          <t>217,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>196,83%</t>
+          <t>196,65%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5,41; 139,09</t>
+          <t>-15,89; 70,12</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-19,54; 108,01</t>
+          <t>-21,49; 63,47</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>131,85; 344,96</t>
+          <t>118,27; 275,02</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-14,66; 64,81</t>
+          <t>9,76; 149,75</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-21,83; 56,56</t>
+          <t>-18,6; 103,52</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>124,88; 270,02</t>
+          <t>131,31; 355,9</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,11; 79,81</t>
+          <t>6,64; 79,29</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-10,63; 55,5</t>
+          <t>-10,57; 56,53</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>140,91; 256,21</t>
+          <t>147,48; 269,67</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>11,16</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-6,87</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>52,32</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>8,96</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>4,9</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>57,29</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>11,16</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-6,87</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>52,46</t>
+          <t>56,98</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>54,89</t>
+          <t>54,59</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 18,72</t>
+          <t>2,02; 19,51</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 13,85</t>
+          <t>-15,23; 1,64</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>51,23; 64,85</t>
+          <t>44,46; 58,76</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,71; 21,04</t>
+          <t>-0,33; 18,77</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-15,71; 1,74</t>
+          <t>-3,6; 14,29</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>45,66; 60,2</t>
+          <t>49,86; 63,62</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,61; 16,36</t>
+          <t>3,79; 16,29</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-7,59; 5,26</t>
+          <t>-7,46; 4,96</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>49,61; 59,67</t>
+          <t>49,71; 59,42</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>26,48%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-16,29%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>124,13%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>22,45%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>12,29%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>143,64%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>26,48%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-16,29%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>124,48%</t>
+          <t>142,85%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>133,86%</t>
+          <t>133,12%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 52,08</t>
+          <t>3,78; 51,78</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-10,07; 38,77</t>
+          <t>-33,23; 3,92</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>110,99; 195,19</t>
+          <t>92,44; 163,28</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,67; 58,38</t>
+          <t>-1,72; 52,88</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-34,67; 4,56</t>
+          <t>-7,97; 40,59</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>95,49; 170,3</t>
+          <t>108,73; 190,1</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,96; 43,65</t>
+          <t>8,75; 43,34</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-17,25; 14,07</t>
+          <t>-16,75; 13,88</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>108,18; 162,04</t>
+          <t>108,72; 162,41</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>9,96</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>6,61</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>42,75</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-0,06</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>2,05</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>45,45</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>9,96</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>6,61</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>42,8</t>
+          <t>45,5</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>44,0</t>
+          <t>43,99</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-12,84; 13,02</t>
+          <t>-3,16; 22,09</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-10,83; 14,34</t>
+          <t>-6,76; 17,73</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>34,26; 55,05</t>
+          <t>31,9; 53,26</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 21,95</t>
+          <t>-12,44; 14,05</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 18,55</t>
+          <t>-10,38; 14,06</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>32,41; 52,71</t>
+          <t>35,0; 55,66</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 13,61</t>
+          <t>-4,06; 13,75</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-4,47; 13,14</t>
+          <t>-5,76; 12,89</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>36,45; 50,34</t>
+          <t>36,3; 51,31</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>21,15%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>14,04%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>90,81%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>-0,13%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>4,64%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>102,7%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>21,15%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>14,04%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>102,81%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,02%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-25,54; 35,63</t>
+          <t>-5,52; 53,8</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-20,58; 39,41</t>
+          <t>-13,42; 42,85</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>64,48; 153,52</t>
+          <t>57,86; 136,28</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 54,11</t>
+          <t>-24,62; 38,69</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-8,06; 46,3</t>
+          <t>-20,11; 39,09</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>58,94; 136,29</t>
+          <t>65,75; 156,27</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-8,2; 33,08</t>
+          <t>-8,74; 32,89</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-8,96; 32,0</t>
+          <t>-10,96; 31,06</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>71,24; 126,7</t>
+          <t>69,14; 130,66</t>
         </is>
       </c>
     </row>
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>-4,77</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>-12,11</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>38,84</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>3,41</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>-5,2</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>42,24</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>-4,77</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>-12,11</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>38,17</t>
+          <t>42,41</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>40,24</t>
+          <t>40,66</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-10,86; 20,01</t>
+          <t>-18,39; 9,34</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-19,08; 7,86</t>
+          <t>-24,97; 3,13</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>31,03; 52,6</t>
+          <t>27,65; 49,2</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-17,23; 8,82</t>
+          <t>-10,36; 19,03</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-25,62; 2,08</t>
+          <t>-18,3; 9,67</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>27,38; 48,66</t>
+          <t>32,15; 53,45</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-10,71; 9,1</t>
+          <t>-10,2; 9,96</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-17,95; 1,99</t>
+          <t>-18,09; 1,69</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>31,13; 48,0</t>
+          <t>32,95; 48,2</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>-8,83%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>-22,43%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>71,93%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>6,83%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>-10,39%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>84,5%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>-8,83%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>-22,43%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>70,68%</t>
+          <t>84,84%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>77,44%</t>
+          <t>78,24%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-19,68; 46,65</t>
+          <t>-30,29; 19,26</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-34,39; 17,88</t>
+          <t>-42,09; 6,64</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>54,44; 127,23</t>
+          <t>45,08; 106,56</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-29,28; 18,35</t>
+          <t>-18,36; 44,35</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-43,45; 3,98</t>
+          <t>-34,32; 21,76</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>45,24; 108,41</t>
+          <t>55,93; 128,92</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-19,0; 20,08</t>
+          <t>-18,18; 20,59</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-32,36; 3,81</t>
+          <t>-32,6; 3,74</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>53,12; 105,73</t>
+          <t>57,01; 107,02</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>5,29</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-1,8</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>51,88</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>6,81</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>2,55</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>55,38</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>5,29</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>-1,8</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>51,88</t>
+          <t>55,15</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>53,58</t>
+          <t>53,47</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>1,5; 11,61</t>
+          <t>0,47; 10,19</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 7,3</t>
+          <t>-6,23; 3,26</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>51,67; 59,27</t>
+          <t>47,92; 55,74</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,42; 10,41</t>
+          <t>1,55; 12,13</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-6,65; 3,11</t>
+          <t>-2,32; 7,78</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>48,22; 55,47</t>
+          <t>50,99; 58,96</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,56; 9,8</t>
+          <t>2,55; 9,69</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 3,59</t>
+          <t>-3,08; 3,81</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>50,76; 56,29</t>
+          <t>50,85; 56,14</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>12,35%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-4,21%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>121,22%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>17,11%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>6,4%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>139,08%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>12,35%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>-4,21%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>121,22%</t>
+          <t>138,52%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>129,58%</t>
+          <t>129,33%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>3,61; 30,65</t>
+          <t>1,0; 25,2</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-6,07; 19,36</t>
+          <t>-13,92; 8,03</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>119,75; 162,79</t>
+          <t>103,19; 140,15</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>0,96; 25,44</t>
+          <t>3,95; 32,29</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-14,65; 7,66</t>
+          <t>-5,54; 20,77</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>104,89; 139,51</t>
+          <t>118,82; 161,82</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>6,19; 24,88</t>
+          <t>5,85; 24,28</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-7,41; 9,16</t>
+          <t>-7,24; 9,48</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>116,14; 144,32</t>
+          <t>117,19; 144,4</t>
         </is>
       </c>
     </row>
